--- a/artfynd/A 26134-2019 artfynd.xlsx
+++ b/artfynd/A 26134-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126992700</v>
+        <v>126573203</v>
       </c>
       <c r="B2" t="n">
-        <v>43043</v>
+        <v>44799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100770</v>
+        <v>201164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre blåvinge</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cupido minimus</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fuessly, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -757,27 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ovanligt sen obs</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126992692</v>
+        <v>126573230</v>
       </c>
       <c r="B3" t="n">
-        <v>44799</v>
+        <v>43043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>201164</v>
+        <v>100770</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Mindre blåvinge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Cupido minimus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fuessly, 1775)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -847,7 +842,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -887,22 +882,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
